--- a/outputs/BAT-2026-NB-00004295-OT_Claims_Analysis.xlsx
+++ b/outputs/BAT-2026-NB-00004295-OT_Claims_Analysis.xlsx
@@ -574,7 +574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Batch: BAT-2026-NB-00004295-OT  |  Period: 01-02-2026 – 28-02-2026  |  Generated: 2026-04-06 11:23</t>
+          <t>Batch: BAT-2026-NB-00004295-OT  |  Period: 01-02-2026 – 28-02-2026  |  Generated: 2026-04-06 12:47</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0f5ac536-ba9a-414b-a490-e46d5ceb2c18</t>
+          <t>8ec03133-93b7-4241-872a-21bdce650dfb</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -27147,14 +27147,14 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>oral</t>
+          <t>professional</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>8ec03133-93b7-4241-872a-21bdce650dfb</t>
+          <t>0f5ac536-ba9a-414b-a490-e46d5ceb2c18</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>oral</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>f34a324c-0ea5-4659-9c6c-ee6f56d5090f</t>
+          <t>da9bbe71-4e7e-4b3a-bee9-ead90b2a8b06</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -27591,7 +27591,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>da9bbe71-4e7e-4b3a-bee9-ead90b2a8b06</t>
+          <t>f34a324c-0ea5-4659-9c6c-ee6f56d5090f</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>3435243a-dec1-44fb-af98-b33b44dd63ff</t>
+          <t>c2ed10c7-3779-4718-85e3-a59e1e546324</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -27768,14 +27768,14 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>oral</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>c2ed10c7-3779-4718-85e3-a59e1e546324</t>
+          <t>3435243a-dec1-44fb-af98-b33b44dd63ff</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>oral</t>
+          <t>professional</t>
         </is>
       </c>
     </row>
@@ -28143,7 +28143,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>a2eeecad-0b4e-4303-8a94-38394da369ed</t>
+          <t>de7fd886-e6b2-427c-bea0-d20a51d5944c</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -28189,7 +28189,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>0309bf45-12b2-4d0d-b717-8293b0069094</t>
+          <t>aaf00592-e859-4ccb-b3dd-569f9fd59173</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -28212,7 +28212,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>de7fd886-e6b2-427c-bea0-d20a51d5944c</t>
+          <t>0309bf45-12b2-4d0d-b717-8293b0069094</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -28235,7 +28235,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>aaf00592-e859-4ccb-b3dd-569f9fd59173</t>
+          <t>a2eeecad-0b4e-4303-8a94-38394da369ed</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
